--- a/光伏配储项目/电价数据/2026/上寨站.xlsx
+++ b/光伏配储项目/电价数据/2026/上寨站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48185</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7555599999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.53967</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5550499999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48306</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47385</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41613</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40617</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47109</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12608</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23228</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.03453</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.20551</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.03287</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.06604</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.14682</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15051</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.13622</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.07486</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.50936</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53759</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7340800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12323</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.19865</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66137</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8658400000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47448</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19663</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41031</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.27346</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.98611</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28238</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.47499</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.73363</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08274</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95401</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89347</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80061</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76148</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51462</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48365</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46471</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42765</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71749</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.89001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9432699999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50292</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52536</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50973</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50987</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49184</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.43066</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40879</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.16451</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.02504</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.08501</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49326</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.49026</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.11065</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12101</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.24845</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.02594</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.5982799999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.04155</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.78091</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.13677</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.22943</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.21119</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5926</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7432300000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.75422</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16161</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.25018</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13031</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83758</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2054</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10629</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25644</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02208</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09051</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6515599999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98341</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9142899999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9575900000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77923</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.88558</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7354299999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.78115</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7260599999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.75926</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45117</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44528</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51335</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4933999999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47799</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44179</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21474</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.00479</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.18246</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78016</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.21386</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.50559</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28554</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62118</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64646</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.4659700000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.54595</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.48269</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61098</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48442</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6177999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.56875</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55723</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7158300000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.60076</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.51738</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55096</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45859</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34236</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5147200000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5033299999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.07809000000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.12005</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56063</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.24694</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17354</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15686</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.11749</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62449</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47484</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48521</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.54848</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5582</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49524</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46956</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50482</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32139</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.08685</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07415000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.15562</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09323000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13151</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.08345</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.00705</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.03706</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.01527</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.005690000000000001</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01887</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.23991</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42558</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4876</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54931</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3729</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.87052</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.46498</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5795800000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.53774</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.55187</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.43816</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.62599</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.43426</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10213</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00498</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1966</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04448</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26124</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15077</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.02734</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05074</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04892000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34819</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32389</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854800000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18704</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86922</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57812</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79095</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54311</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6730700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.82039</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88446</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47139</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.50169</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6723899999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.50187</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.05812</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.81338</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8753200000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.52006</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.9165800000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.84701</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5904299999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.48434</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.54579</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48806</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.43027</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37294</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93716</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.53264</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47901</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5572999999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.47303</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.6206199999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.21857</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.08703</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26782</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2009</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.45189</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.5394500000000001</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47561</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.48022</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.46649</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.46838</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.7945800000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.95108</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48456</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20497</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.73181</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8238</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6829299999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.81677</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.6057100000000001</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47775</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52883</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.5013500000000001</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44161</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.48185</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.62118</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43667</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45903</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48875</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.51913</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.55564</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.5272100000000001</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43662</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43279</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.51675</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47892</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5186799999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.4660899999999999</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63532</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.57423</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25183</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01738</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28464</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.65766</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.55379</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.03216</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.56052</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.52696</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.42062</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.51448</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43361</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40796</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37271</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5245700000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.43398</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.52328</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.56628</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.50331</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.45216</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09737</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.11481</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08176</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.08948</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10084</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.22969</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08491</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25637</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12548</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.02679</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06262</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05428</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16025</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07299</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42913</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45885</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5502999999999999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46796</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.45049</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.47105</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.46099</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.54922</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.5353600000000001</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.5311699999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.53783</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46332</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.39289</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.68768</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.57263</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49915</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43372</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44645</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54849</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23428</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17247</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21363</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.23969</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25788</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5278400000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39647</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.63995</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.64728</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.13523</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4362200000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67963</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51828</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47085</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46482</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17576</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.19087</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25631</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.13288</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43683</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48219</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46771</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72105</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.06936</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.90908</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.7333999999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42919</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5214099999999999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.43973</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.44083</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.41028</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.48175</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43341</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.51212</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.42522</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36944</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.6081799999999999</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42613</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43601</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.67574</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.09344</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.5270499999999999</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.55087</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37564</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.10721</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.20043</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.12391</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.22086</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.25158</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.15251</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.21602</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.25774</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.57148</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.51301</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47169</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68192</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63948</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.65463</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84972</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.62722</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.21335</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.6802699999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52561</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43733</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.61142</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.50722</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4884</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41796</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.39108</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.59611</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.73451</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6377999999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.9160900000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.48133</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.48319</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45813</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.47286</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.46604</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.48122</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43876</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40787</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.49165</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48865</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.44462</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47557</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46481</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.48099</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.47012</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5637300000000001</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.55128</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7387400000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62961</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5442899999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6184400000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.54028</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4652</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54816</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45439</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.42099</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6474500000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.47482</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.51173</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.6031799999999999</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.5412400000000001</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6430499999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.64546</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.71256</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.96127</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.19218</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.31007</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.9449500000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.11643</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.92961</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.70431</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.16018</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7892100000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.64278</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69212</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.56677</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.59639</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59315</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.58109</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5727599999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.70216</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.52261</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.54791</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.53263</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43587</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45672</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.58153</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.47162</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45375</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.4382200000000001</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41867</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.62983</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.46018</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.46191</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.06002</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.03105</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.44148</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.51837</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.02337</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.10208</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.02829</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43305</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.49403</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.47424</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45539</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43725</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.52642</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46948</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.50892</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.52464</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.5016499999999999</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47908</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.47496</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.5157200000000001</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.48972</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.53364</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.51406</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.47062</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.42496</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6304299999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.48259</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49681</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.50322</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.48638</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.6347</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.60354</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.59751</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.6116900000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.4723</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.5721900000000001</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44834</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45976</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.55674</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.55492</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.5718099999999999</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.49939</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.57182</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.17903</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.20744</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.20978</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22858</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.07196999999999999</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.08617</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.10536</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18056</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22167</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27395</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21334</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46307</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.45707</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.47605</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44284</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.49475</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50995</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46874</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.42895</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.52436</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.51767</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.52903</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.51988</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.5198700000000001</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.51354</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.51354</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.5173300000000001</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.5213099999999999</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.51354</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.51416</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.52934</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.52889</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.53235</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03434</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00099</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15169</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02286</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01488</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02949</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03705</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03617</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01489</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03556</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.52499</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.54373</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.41234</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.20113</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.03009</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49687</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.89022</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.53027</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.54477</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.6003500000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.45415</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.5148200000000001</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.47598</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.48915</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.6479</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.47002</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44365</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.67065</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.5804900000000001</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.6624500000000001</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.6059</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.6637799999999999</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.63163</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.61311</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.63837</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6807799999999999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46652</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.54427</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.6039800000000001</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52655</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.53142</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.42595</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.91211</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87371</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.04853</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.01696</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.03835</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-3e-05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.00962</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04842</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.04738000000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.00393</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.0541</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.16786</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.12479</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00126</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.15335</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.05489</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.16011</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8637999999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.86205</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8661799999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.15605</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.15609</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.15004</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.4242</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.60958</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.9028099999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.49621</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.84793</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5197999999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.6293099999999999</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.52415</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.49066</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.53684</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6728200000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.47762</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.46458</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.63167</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.5432899999999999</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.51301</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.51031</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.67923</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.50107</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5285299999999999</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.00208</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.21292</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.15588</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.22918</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.43102</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.63524</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.26124</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.92448</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.61811</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.55183</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.54255</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.49205</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.68235</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.40543</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.50037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.51766</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48725</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.48148</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45747</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55291</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.86749</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.02073</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.84782</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.7866299999999999</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.60521</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.02071</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.83275</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46658</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46927</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58508</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55798</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6609400000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81676</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5764600000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.81621</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.6165900000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.61942</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.46918</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.54592</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5435099999999999</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40443</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5323300000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.44055</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44619</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45584</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.71569</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.78984</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.54863</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.78322</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.62575</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9529500000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5370900000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55086</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.02343</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.48444</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49771</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40871</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.62451</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17737</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27186</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17444</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20768</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09876</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18574</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01543</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05681</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26497</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02833</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04218</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11099</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02613</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00171</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23282</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18331</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20838</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.44007</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.54787</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.46058</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.52189</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47539</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42777</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.4209</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.27012</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.23849</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.46963</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43695</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40589</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.13591</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.41111</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.44346</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.42248</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.39001</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40667</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40796</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17692</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14655</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19981</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02351</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24191</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03436</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.02671</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.00652</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.02047</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.02438</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13175</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.06356000000000001</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17476</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.01291</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22722</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25768</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.02249</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22183</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.03974</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19979</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14797</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25916</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41822</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43197</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43137</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51154</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42141</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41759</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40922</v>
       </c>
     </row>
   </sheetData>
